--- a/docs/table/核价测试数据/核价系统功能基础数据功能结构所需字段（导入版本)-新版-测试罗克韦尔-版本测试.xlsx
+++ b/docs/table/核价测试数据/核价系统功能基础数据功能结构所需字段（导入版本)-新版-测试罗克韦尔-版本测试.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\核价测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE5E3EF-8C91-489E-B2DD-1E6E2C447B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F4DEDF-B2A3-49AA-9E54-2E82B48E410D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" firstSheet="9" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素核价价格表" sheetId="11" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="257">
   <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4032,9 +4032,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20">
+      <c r="A2" s="20">
         <v>3120014539</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>252</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>201</v>
